--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -380,7 +380,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -471,7 +471,7 @@
     <t>diseaseOutcome</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseaseOutcome}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseaseOutcome|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -637,7 +637,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -667,7 +667,7 @@
 このプロファイルではHL70421 Severity of Illness Code（MI 軽度, MO 中度, SE 重度）を採用。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS|1.1.0</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -710,7 +710,7 @@
     <t>状態や診断の特定</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -783,7 +783,7 @@
     <t>diseasePrefixModifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseasePrefixModifier}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseasePrefixModifier|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -800,7 +800,7 @@
     <t>diseasePostfixModifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseasePostfixModifier}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseasePostfixModifier|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -862,7 +862,7 @@
     <t>JP_Disease_MEDIS_Concept_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://medis.or.jp/ValueSet/master-disease-exCode</t>
+    <t>http://medis.or.jp/ValueSet/master-disease-exCode|1.1.0</t>
   </si>
   <si>
     <t>Condition.code.coding:medisExchange.id</t>
@@ -1022,7 +1022,7 @@
     <t>JP_Disease_MEDIS_ManagementID_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://medis.or.jp/ValueSet/master-disease-keyNumber</t>
+    <t>http://medis.or.jp/ValueSet/master-disease-keyNumber|1.1.0</t>
   </si>
   <si>
     <t>Condition.code.coding:medisRecordNo.id</t>
@@ -1064,7 +1064,7 @@
     <t>JP_Disease_Claim_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/masterB-disease</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/masterB-disease|1.1.0</t>
   </si>
   <si>
     <t>Condition.code.coding:receipt.id</t>
@@ -1106,7 +1106,7 @@
     <t>JP_ConditionDiseaseCodeICD10_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/ICD10-2013-full</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/ICD10-2013-full|1.1.0</t>
   </si>
   <si>
     <t>Condition.code.coding:icd10.id</t>
@@ -1169,7 +1169,7 @@
     <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1188,7 +1188,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1216,7 +1216,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1318,7 +1318,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1338,7 +1338,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1426,7 +1426,7 @@
     <t>状態段階を説明するコード（例：がんの段階）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1439,7 +1439,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
+    <t xml:space="preserve">Reference(ClinicalImpression|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1464,7 +1464,7 @@
     <t>状態分類を表すコード（例：臨床的または病理学的）。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1511,7 +1511,7 @@
     <t>症状や現れ方を記述するコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1530,7 +1530,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1892,7 +1892,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="187.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1907,7 +1907,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="26.36328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.23828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -380,7 +380,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -471,7 +471,7 @@
     <t>diseaseOutcome</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseaseOutcome|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseaseOutcome}
 </t>
   </si>
   <si>
@@ -637,7 +637,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -667,7 +667,7 @@
 このプロファイルではHL70421 Severity of Illness Code（MI 軽度, MO 中度, SE 重度）を採用。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -710,7 +710,7 @@
     <t>状態や診断の特定</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -783,7 +783,7 @@
     <t>diseasePrefixModifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseasePrefixModifier|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseasePrefixModifier}
 </t>
   </si>
   <si>
@@ -800,7 +800,7 @@
     <t>diseasePostfixModifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseasePostfixModifier|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Condition_DiseasePostfixModifier}
 </t>
   </si>
   <si>
@@ -862,7 +862,7 @@
     <t>JP_Disease_MEDIS_Concept_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://medis.or.jp/ValueSet/master-disease-exCode|1.1.0</t>
+    <t>http://medis.or.jp/ValueSet/master-disease-exCode</t>
   </si>
   <si>
     <t>Condition.code.coding:medisExchange.id</t>
@@ -1022,7 +1022,7 @@
     <t>JP_Disease_MEDIS_ManagementID_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://medis.or.jp/ValueSet/master-disease-keyNumber|1.1.0</t>
+    <t>http://medis.or.jp/ValueSet/master-disease-keyNumber</t>
   </si>
   <si>
     <t>Condition.code.coding:medisRecordNo.id</t>
@@ -1064,7 +1064,7 @@
     <t>JP_Disease_Claim_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/masterB-disease|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/masterB-disease</t>
   </si>
   <si>
     <t>Condition.code.coding:receipt.id</t>
@@ -1106,7 +1106,7 @@
     <t>JP_ConditionDiseaseCodeICD10_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/ICD10-2013-full|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/ICD10-2013-full</t>
   </si>
   <si>
     <t>Condition.code.coding:icd10.id</t>
@@ -1169,7 +1169,7 @@
     <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1188,7 +1188,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -1216,7 +1216,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1318,7 +1318,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1338,7 +1338,7 @@
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
 </t>
   </si>
   <si>
@@ -1426,7 +1426,7 @@
     <t>状態段階を説明するコード（例：がんの段階）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1439,7 +1439,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(ClinicalImpression|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
 </t>
   </si>
   <si>
@@ -1464,7 +1464,7 @@
     <t>状態分類を表すコード（例：臨床的または病理学的）。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1511,7 +1511,7 @@
     <t>症状や現れ方を記述するコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1530,7 +1530,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1892,7 +1892,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="187.28515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1907,7 +1907,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="26.36328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.23828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
